--- a/Random.xlsx
+++ b/Random.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d268e4ab35f8c14a/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kalyan\GitHub\Cloned Repository\Excel-Mini-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB980AE6-A1B2-430E-8C2A-12130EF32E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{275562D1-533C-475F-9917-06B8C594C5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{001AC5ED-BEAC-4A7B-A9BF-60A48BFA4516}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Agent Name</t>
   </si>
@@ -48,6 +48,15 @@
   </si>
   <si>
     <t>Weekoffs</t>
+  </si>
+  <si>
+    <t>Panneeru Kalyan</t>
+  </si>
+  <si>
+    <t>kpanne1</t>
+  </si>
+  <si>
+    <t>Wed - Thu</t>
   </si>
 </sst>
 </file>
@@ -419,10 +428,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DFDA23A-C7E3-4665-8488-CDCF811615E8}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -438,6 +447,17 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
